--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_380_Italy_mainland.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_380_Italy_mainland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rcb7ecfa3d64847ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R8a62a8f67b0f47c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rf843d3b413cb4418"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rf16bffbf41b14745"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R457fbc1fe3eb4cf0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R3dba109e2b7140f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Ra6a11be48cca4343"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rb74d6a00984f4c13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rf49dabad76aa411f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R5d29f2600d0747a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Ra757b5d1c691474b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R89805483853841f5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ380CommercialTable" displayName="EEZ380CommercialTable" ref="A1:O13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O13"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ380CommercialTable" displayName="EEZ380CommercialTable" ref="A1:E13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E13"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ380FunctionalTable" displayName="EEZ380FunctionalTable" ref="A1:O26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O26"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ380FunctionalTable" displayName="EEZ380FunctionalTable" ref="A1:E26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E26"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ380ValidationTable" displayName="EEZ380ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ380ValidationTable" displayName="EEZ380ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -11347,7 +11301,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99193810fa7641e9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R986b3ba6b1b9419f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11357,20 +11311,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -11378,714 +11322,250 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>37374.459049266</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>37374.459049266</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$160,A2,'Species'!$U$2:$U$160))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>4814763.0114990305</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>4814763.0114990305</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>9148.525733494002</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.348065754216404</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2228.772570320541</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>9148.525733494002</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2371.438315481548</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$160,A3,'Species'!$U$2:$U$160))</x:f>
-        <x:v>21695164.45457661</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.348065754216404</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2228.772570320541</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>20389983.21368304</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>1305181.2408935726</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0640109031584541</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.06401090315845424</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>12697.5916607305</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.3406833730059913</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>219.12068303048923</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>12697.5916607305</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>272.35789180194035</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$160,A4,'Species'!$U$2:$U$160))</x:f>
-        <x:v>3458289.2956784577</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.3406833730059913</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>219.12068303048923</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>2782304.9575415114</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>675984.3381369463</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.2429583918558866</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.24295839185588655</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>3328.20837952</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.393702201085204</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>247.57238534414148</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>3328.20837952</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>418.6316593958918</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$160,A5,'Species'!$U$2:$U$160))</x:f>
-        <x:v>1393293.3967337697</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.393702201085204</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>247.57238534414148</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>823972.4874401261</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>569320.9092936435</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.6909465036416198</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.6909465036416197</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>28863.7538201061</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.062489996023823</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>115.47553845854004</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>28863.7538201061</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>115.82398927564074</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$160,A6,'Species'!$U$2:$U$160))</x:f>
-        <x:v>3343115.1129147033</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.062489996023823</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>115.47553845854004</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>3333057.514311494</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>10057.59860320948</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0030175292685541</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.0030175292685542116</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>19883.155885279</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.2310330575029913</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>17.02288077739992</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>19883.155885279</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>32.37693178088109</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$160,A7,'Species'!$U$2:$U$160))</x:f>
-        <x:v>643755.5816863024</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.2310330575029913</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>17.02288077739992</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>338468.592113562</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>305286.98957274045</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.901965490110561</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.9019654901105608</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>25906.292602037705</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.6971870504876962</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>497.9515063467897</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>25906.292602037705</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>698.4831837753036</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$160,A8,'Species'!$U$2:$U$160))</x:f>
-        <x:v>18095109.73648589</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.6971870504876962</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>497.9515063467897</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>12900077.42504537</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>5195032.311440522</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.4027132659959405</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.40271326599594043</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>64287.73016486559</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.4175935402195026</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>261.57337754973963</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>64287.73016486559</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>519.3562079949029</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$160,A9,'Species'!$U$2:$U$160))</x:f>
-        <x:v>33388231.75902413</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.4175935402195026</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>261.57337754973963</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>16815958.714230172</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>16572273.044793956</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.9855086662867456</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.9855086662867457</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>18.964896661</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.35</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>223.872113856834</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>18.964896661</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>223.872113856834</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$160,A10,'Species'!$U$2:$U$160))</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>4245.711504574483</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.35</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>223.872113856834</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
-        <x:v>4245.711504574483</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>4207.384685032202</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.9708939007278796</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>935.1771800190851</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>4207.384685032202</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>993.4945153535659</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$160,A11,'Species'!$U$2:$U$160))</x:f>
-        <x:v>4180013.6085620825</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.9708939007278796</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>935.1771800190851</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>3934650.145003901</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>245363.46355818165</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.062359664650169</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.06235966465016889</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>3020.8227425258</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.1144582694823315</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>1301.542246890754</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>3020.8227425258</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>1605.5874637496934</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$160,A12,'Species'!$U$2:$U$160))</x:f>
-        <x:v>4850195.125609392</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.1144582694823315</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>1301.542246890754</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>3931728.4197657197</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>918466.7058436726</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.233603801632464</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.23360380163246408</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>25740.705051943503</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.429375420812637</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>2687.6667640312826</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>25740.705051943503</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>2736.0932252230828</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$H$2:$H$160,A13,'Species'!$U$2:$U$160))</x:f>
-        <x:v>70428968.7050882</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.429375420812637</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>2687.6667640312826</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>69182437.45084068</x:v>
       </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>1246531.2542475164</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0180180303004396</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.018018030300439622</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G13">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O13">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49bcb50855b743da"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raacbf817ad2d4e8f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12095,20 +11575,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -12116,1416 +11586,497 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>14757.3954081492</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.787187953096628</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>612.6154608555781</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>14757.3954081492</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>663.9471588255407</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$160,A2,'Species'!$U$2:$U$160))</x:f>
-        <x:v>9798130.752905741</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.787187953096628</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>612.6154608555781</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>9040608.588991314</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>757522.1639144272</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0837910585839161</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.0837910585839162</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>1463.166026164</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.8205147624905043</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>661.4770219564585</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>1463.166026164</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>662.3596228041454</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$160,A3,'Species'!$U$2:$U$160))</x:f>
-        <x:v>969142.0971898274</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.8205147624905043</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>661.4770219564585</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>967850.7056148284</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>1291.3915749989683</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0013342879924634</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.0013342879924632695</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>5576.569886219</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>2.8055874178407216</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>63.91273724437783</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>5576.569886219</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>930.1634540040626</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$160,A4,'Species'!$U$2:$U$160))</x:f>
-        <x:v>5187121.506860508</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>2.8055874178407216</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>63.91273724437783</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>356413.84586282494</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>4830707.660997683</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>14.553647584322258</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>13.55364758432226</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>8191.0584771101</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.340096089160231</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>2188.245727348695</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>8191.0584771101</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2369.9564583991146</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$160,A5,'Species'!$U$2:$U$160))</x:f>
-        <x:v>19412451.9389519</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.340096089160231</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>2188.245727348695</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>17924048.714999482</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>1488403.2239524163</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.083039454289525</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.08303945428952486</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>271.19865030700004</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.36</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2290.867652767775</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>271.19865030700004</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2290.867652767775</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$160,A6,'Species'!$U$2:$U$160))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>621280.2154625858</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.36</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2290.867652767775</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>621280.2154625858</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>21371.5523811049</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.409183668712593</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>2565.568819111957</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>21371.5523811049</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2609.246657196454</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$160,A7,'Species'!$U$2:$U$160))</x:f>
-        <x:v>55763651.60949688</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.409183668712593</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>2565.568819111957</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>54830188.40498063</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>933463.2045162469</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.017024621502695</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.01702462150269492</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>545.9556095288</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.887325622901176</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>771.4816895202141</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>545.9556095288</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>884.1565306308714</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$160,A8,'Species'!$U$2:$U$160))</x:f>
-        <x:v>482710.21759944654</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.887325622901176</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>771.4816895202141</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>421194.7560423169</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>61515.46155712963</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.1460499226893253</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.14604992268932535</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>1430.9720084248002</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.254533223790709</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1796.9385418014679</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>1430.9720084248002</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>2185.7652248981603</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$160,A9,'Species'!$U$2:$U$160))</x:f>
-        <x:v>3127768.8538176054</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.254533223790709</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1796.9385418014679</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>2571368.7541775783</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>556400.0996400272</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.2163828500817204</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.21638285008172042</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>1354.1295492469999</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.239459567387304</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1735.6396681098247</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>1354.1295492469999</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>2164.1094617177873</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$160,A10,'Species'!$U$2:$U$160))</x:f>
-        <x:v>2930484.569917075</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.239459567387304</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1735.6396681098247</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>2350280.9614327694</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>580203.6084843054</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.246865637770645</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.24686563777064505</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>1371.610939051</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>2.881912261640582</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>76.19250665348304</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>1371.610939051</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>77.27824255759502</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$160,A11,'Species'!$U$2:$U$160))</x:f>
-        <x:v>105995.68284263386</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>2.881912261640582</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>76.19250665348304</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>104506.47559963344</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>1489.207243000419</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0142499039839943</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.014249903983994295</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>1369.4448917422</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.390260198037526</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>2456.180041481221</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>1369.4448917422</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>2695.8254154438546</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$160,A12,'Species'!$U$2:$U$160))</x:f>
-        <x:v>3691784.3442083807</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.390260198037526</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>2456.180041481221</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>3363603.211005603</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>328181.1332027777</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0975683255768633</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.09756832557686336</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>37.2599518834</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.08</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>1202.2644346174131</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>37.2599518834</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>1202.2644346174131</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$160,A13,'Species'!$U$2:$U$160))</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>44796.31498496792</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.08</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>1202.2644346174131</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
-        <x:v>44796.31498496792</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>14241.616087127</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.484196098699917</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>304.9271528424669</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>14241.616087127</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>462.3572908963927</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$160,A14,'Species'!$U$2:$U$160))</x:f>
-        <x:v>6584715.032030525</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.484196098699917</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>304.9271528424669</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>4342655.445323111</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>2242059.586707414</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.5162876988369027</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.5162876988369028</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>23963.744119929295</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.272943032743836</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>187.47485775024444</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>23963.744119929295</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>297.2286264461382</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$160,A15,'Species'!$U$2:$U$160))</x:f>
-        <x:v>7122710.749273306</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.272943032743836</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>187.47485775024444</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>4492599.520047002</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>2630111.229226304</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.5854319347830024</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.5854319347830025</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>28979.364819229104</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.8737436302021773</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>747.727976454809</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>28979.364819229104</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>1138.271835253254</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$160,A16,'Species'!$U$2:$U$160))</x:f>
-        <x:v>32986394.777257495</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.8737436302021773</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>747.727976454809</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>21668681.81522786</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>11317712.962029636</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.52230740469298</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.5223074046929801</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>1152.58781572</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>2.8640418964206122</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>73.12096199268507</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>1152.58781572</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>159.10485845129898</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$160,A17,'Species'!$U$2:$U$160))</x:f>
-        <x:v>183382.32127282248</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>2.8640418964206122</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>73.12096199268507</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>84278.32986649402</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>99103.99140632845</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>2.1759130913405604</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>1.1759130913405602</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>19946.766976518</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>2.2312529960262024</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>17.031503809935472</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>19946.766976518</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>32.33731013037247</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$160,A18,'Species'!$U$2:$U$160))</x:f>
-        <x:v>645024.7898179346</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>2.2312529960262024</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>17.031503809935472</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>339723.4377564614</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>305301.35206147324</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.8986761528073774</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.8986761528073773</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>11325.980721679502</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.3962419590863027</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>249.02443251444282</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>11325.980721679502</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>295.9826345474055</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$160,A19,'Species'!$U$2:$U$160))</x:f>
-        <x:v>3352293.612835824</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.3962419590863027</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>249.02443251444282</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>2820445.9218857572</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>531847.6909500668</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.1885686539220977</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.18856865392209757</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>1778.121556621</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.3878333778521807</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>244.2493281847427</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>1778.121556621</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>245.80751108080824</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$160,A20,'Species'!$U$2:$U$160))</x:f>
-        <x:v>437075.6342321405</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.3878333778521807</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>244.2493281847427</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>434304.9956354882</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>2770.6385966523085</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.0063794766914855</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.006379476691485499</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>1795.718294578</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.868956011651014</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>739.5303665140882</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>1795.718294578</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>1009.5098774880247</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$160,A21,'Species'!$U$2:$U$160))</x:f>
-        <x:v>1812795.3555624415</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.868956011651014</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>739.5303665140882</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>1327988.2085453218</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>484807.1470171197</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.3650688642395232</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.36506886423952317</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>66392.42384845811</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.0895543227380684</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>122.90069044995548</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>66392.42384845811</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>123.24175626101011</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$160,A22,'Species'!$U$2:$U$160))</x:f>
-        <x:v>8182318.91750935</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.0895543227380684</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>122.90069044995548</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>8159674.731621592</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>22644.18588775769</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1.0027751334008455</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0.002775133400845447</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>2983.209339707</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>3.242267022105446</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>174.689588622132</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>2983.209339707</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>215.9093153124087</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$160,A23,'Species'!$U$2:$U$160))</x:f>
-        <x:v>644102.6859697212</x:v>
-      </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>3.242267022105446</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>174.689588622132</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>521135.6123271178</x:v>
-      </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>122967.07364260335</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1.2359598360463162</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0.23595983604631626</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="18" customHeight="1">
       <x:c r="A24" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B24" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C24" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D24" s="31" t="n">
+      <x:c r="B24" s="31" t="n">
         <x:v>3057.009729213</x:v>
       </x:c>
+      <x:c r="C24" s="32" t="n">
+        <x:v>3.307978346052598</x:v>
+      </x:c>
+      <x:c r="D24" s="32" t="n">
+        <x:f>IF(C24="","",(1/'Metadata'!$B$5)^(C24-1))</x:f>
+        <x:v>203.22556800270473</x:v>
+      </x:c>
       <x:c r="E24" s="31" t="n">
-        <x:v>3057.009729213</x:v>
-      </x:c>
-      <x:c r="F24" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H24" s="32" t="n">
-        <x:f>IF(E24=0,"",I24/E24)</x:f>
-        <x:v>252.53867329690573</x:v>
-      </x:c>
-      <x:c r="I24" s="31" t="n">
-        <x:f>IF(C24=0,"",SUMIF('Species'!$G$2:$G$160,A24,'Species'!$U$2:$U$160))</x:f>
-        <x:v>772013.181271184</x:v>
-      </x:c>
-      <x:c r="J24" s="32" t="n">
-        <x:v>3.307978346052598</x:v>
-      </x:c>
-      <x:c r="K24" s="32" t="n">
-        <x:f>IF(J24="","",(1/'Metadata'!$B$5)^(J24-1))</x:f>
-        <x:v>203.22556800270473</x:v>
-      </x:c>
-      <x:c r="L24" s="31" t="n">
-        <x:f>IF(E24=0,"",E24*K24)</x:f>
+        <x:f>IF(B24=0,"",B24*D24)</x:f>
         <x:v>621262.5386091064</x:v>
-      </x:c>
-      <x:c r="M24" s="31" t="n">
-        <x:f>IF(E24=0,"",I24-L24)</x:f>
-        <x:v>150750.64266207756</x:v>
-      </x:c>
-      <x:c r="N24" s="32" t="n">
-        <x:f>IF(L24=0,"",I24/L24)</x:f>
-        <x:v>1.2426520726641281</x:v>
-      </x:c>
-      <x:c r="O24" s="34" t="n">
-        <x:f>IF(L24=0,"",M24/L24)</x:f>
-        <x:v>0.24265207266412805</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="18" customHeight="1">
       <x:c r="A25" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B25" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C25" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D25" s="31" t="n">
+      <x:c r="B25" s="31" t="n">
         <x:v>101.314179815</x:v>
       </x:c>
+      <x:c r="C25" s="32" t="n">
+        <x:v>3.5722764051597826</x:v>
+      </x:c>
+      <x:c r="D25" s="32" t="n">
+        <x:f>IF(C25="","",(1/'Metadata'!$B$5)^(C25-1))</x:f>
+        <x:v>373.4877871262962</x:v>
+      </x:c>
       <x:c r="E25" s="31" t="n">
-        <x:v>101.314179815</x:v>
-      </x:c>
-      <x:c r="F25" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G25" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H25" s="32" t="n">
-        <x:f>IF(E25=0,"",I25/E25)</x:f>
-        <x:v>400.36317132875564</x:v>
-      </x:c>
-      <x:c r="I25" s="31" t="n">
-        <x:f>IF(C25=0,"",SUMIF('Species'!$G$2:$G$160,A25,'Species'!$U$2:$U$160))</x:f>
-        <x:v>40562.4663313052</x:v>
-      </x:c>
-      <x:c r="J25" s="32" t="n">
-        <x:v>3.5722764051597826</x:v>
-      </x:c>
-      <x:c r="K25" s="32" t="n">
-        <x:f>IF(J25="","",(1/'Metadata'!$B$5)^(J25-1))</x:f>
-        <x:v>373.4877871262962</x:v>
-      </x:c>
-      <x:c r="L25" s="31" t="n">
-        <x:f>IF(E25=0,"",E25*K25)</x:f>
+        <x:f>IF(B25=0,"",B25*D25)</x:f>
         <x:v>37839.608823620016</x:v>
-      </x:c>
-      <x:c r="M25" s="31" t="n">
-        <x:f>IF(E25=0,"",I25-L25)</x:f>
-        <x:v>2722.857507685185</x:v>
-      </x:c>
-      <x:c r="N25" s="32" t="n">
-        <x:f>IF(L25=0,"",I25/L25)</x:f>
-        <x:v>1.0719578661707925</x:v>
-      </x:c>
-      <x:c r="O25" s="34" t="n">
-        <x:f>IF(L25=0,"",M25/L25)</x:f>
-        <x:v>0.07195786617079242</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="18" customHeight="1">
       <x:c r="A26" s="24" t="str">
         <x:v>Small to medium sharks (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B26" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C26" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D26" s="31" t="n">
+      <x:c r="B26" s="31" t="n">
         <x:v>1019.4234039350001</x:v>
       </x:c>
+      <x:c r="C26" s="32" t="n">
+        <x:v>4.123941181271336</x:v>
+      </x:c>
+      <x:c r="D26" s="32" t="n">
+        <x:f>IF(C26="","",(1/'Metadata'!$B$5)^(C26-1))</x:f>
+        <x:v>1330.274239915441</x:v>
+      </x:c>
       <x:c r="E26" s="31" t="n">
-        <x:v>1019.4234039350001</x:v>
-      </x:c>
-      <x:c r="F26" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G26" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H26" s="32" t="n">
-        <x:f>IF(E26=0,"",I26/E26)</x:f>
-        <x:v>1369.8310891934414</x:v>
-      </x:c>
-      <x:c r="I26" s="31" t="n">
-        <x:f>IF(C26=0,"",SUMIF('Species'!$G$2:$G$160,A26,'Species'!$U$2:$U$160))</x:f>
-        <x:v>1396437.8717615667</x:v>
-      </x:c>
-      <x:c r="J26" s="32" t="n">
-        <x:v>4.123941181271336</x:v>
-      </x:c>
-      <x:c r="K26" s="32" t="n">
-        <x:f>IF(J26="","",(1/'Metadata'!$B$5)^(J26-1))</x:f>
-        <x:v>1330.274239915441</x:v>
-      </x:c>
-      <x:c r="L26" s="31" t="n">
-        <x:f>IF(E26=0,"",E26*K26)</x:f>
+        <x:f>IF(B26=0,"",B26*D26)</x:f>
         <x:v>1356112.693821644</x:v>
       </x:c>
-      <x:c r="M26" s="31" t="n">
-        <x:f>IF(E26=0,"",I26-L26)</x:f>
-        <x:v>40325.17793992278</x:v>
-      </x:c>
-      <x:c r="N26" s="32" t="n">
-        <x:f>IF(L26=0,"",I26/L26)</x:f>
-        <x:v>1.02973586053994</x:v>
-      </x:c>
-      <x:c r="O26" s="34" t="n">
-        <x:f>IF(L26=0,"",M26/L26)</x:f>
-        <x:v>0.02973586053994002</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G26">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O26">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2dc63c444434c0a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e4ca3375ff641d8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13700,7 +12251,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -13799,7 +12350,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>166295145.49936318</x:v>
+        <x:v>139251647.64297917</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -13813,7 +12364,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>166295145.49936315</x:v>
+        <x:v>138802843.8086451</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -13827,7 +12378,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-27043497.85638401</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -13841,7 +12392,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>-2.9802322387695312e-8</x:v>
+        <x:v>-27492301.690718085</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -13852,9 +12403,9 @@
         <x:v>EEZ_380</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -13866,47 +12417,19 @@
         <x:v>EEZ_380</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_380</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_380</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re619f8f4f7d64dad"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re7141d287a6f4f5a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13953,7 +12476,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
